--- a/Sample_run/1/student/dungdvhe181404/TC5/GradeDetail.xlsx
+++ b/Sample_run/1/student/dungdvhe181404/TC5/GradeDetail.xlsx
@@ -1059,7 +1059,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>35878</x:v>
+        <x:v>33764</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
@@ -1118,7 +1118,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>35878</x:v>
+        <x:v>33764</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>46</x:v>
@@ -1171,7 +1171,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>35878</x:v>
+        <x:v>33764</x:v>
       </x:c>
       <x:c r="Q4" s="0">
         <x:v>4000</x:v>
@@ -1227,7 +1227,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>35878</x:v>
+        <x:v>33764</x:v>
       </x:c>
       <x:c r="Q5" s="0">
         <x:v>4000</x:v>
@@ -1286,7 +1286,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q6" s="0">
-        <x:v>35878</x:v>
+        <x:v>33764</x:v>
       </x:c>
       <x:c r="R6" s="2" t="s">
         <x:v>46</x:v>
@@ -1342,7 +1342,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q7" s="0">
-        <x:v>35878</x:v>
+        <x:v>33764</x:v>
       </x:c>
       <x:c r="R7" s="3" t="s">
         <x:v>56</x:v>
@@ -1395,7 +1395,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P8" s="0">
-        <x:v>35878</x:v>
+        <x:v>33764</x:v>
       </x:c>
       <x:c r="Q8" s="0">
         <x:v>4000</x:v>
@@ -1454,7 +1454,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>35878</x:v>
+        <x:v>33764</x:v>
       </x:c>
       <x:c r="R9" s="4" t="s">
         <x:v>60</x:v>
@@ -1507,7 +1507,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P10" s="0">
-        <x:v>35878</x:v>
+        <x:v>33764</x:v>
       </x:c>
       <x:c r="Q10" s="0">
         <x:v>4000</x:v>
@@ -1566,7 +1566,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q11" s="0">
-        <x:v>35878</x:v>
+        <x:v>33764</x:v>
       </x:c>
       <x:c r="R11" s="4" t="s">
         <x:v>60</x:v>
